--- a/Startup expansion Data analysis & Visualisation_project/Startup-new.xlsx
+++ b/Startup expansion Data analysis & Visualisation_project/Startup-new.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
         <v>48610</v>
       </c>
       <c r="I2" t="n">
-        <v>1868.896578239139</v>
+        <v>1768.896578239139</v>
       </c>
       <c r="J2" t="n">
         <v>46009</v>
@@ -565,7 +565,7 @@
         <v>45689</v>
       </c>
       <c r="I3" t="n">
-        <v>1675.430876420975</v>
+        <v>1575.430876420975</v>
       </c>
       <c r="J3" t="n">
         <v>42962</v>
@@ -611,7 +611,7 @@
         <v>49554</v>
       </c>
       <c r="I4" t="n">
-        <v>1790.245664739884</v>
+        <v>1690.245664739884</v>
       </c>
       <c r="J4" t="n">
         <v>46786</v>
@@ -657,7 +657,7 @@
         <v>38284</v>
       </c>
       <c r="I5" t="n">
-        <v>1387.604204421892</v>
+        <v>1287.604204421892</v>
       </c>
       <c r="J5" t="n">
         <v>35525</v>
@@ -703,7 +703,7 @@
         <v>59887</v>
       </c>
       <c r="I6" t="n">
-        <v>2087.38236319275</v>
+        <v>1987.38236319275</v>
       </c>
       <c r="J6" t="n">
         <v>57018</v>
@@ -749,7 +749,7 @@
         <v>53827</v>
       </c>
       <c r="I7" t="n">
-        <v>1747.62987012987</v>
+        <v>1647.62987012987</v>
       </c>
       <c r="J7" t="n">
         <v>50747</v>
@@ -795,7 +795,7 @@
         <v>60338</v>
       </c>
       <c r="I8" t="n">
-        <v>1940.128617363344</v>
+        <v>1840.128617363344</v>
       </c>
       <c r="J8" t="n">
         <v>57228</v>
@@ -841,7 +841,7 @@
         <v>19569</v>
       </c>
       <c r="I9" t="n">
-        <v>754.685692248361</v>
+        <v>654.685692248361</v>
       </c>
       <c r="J9" t="n">
         <v>16976</v>
@@ -887,7 +887,7 @@
         <v>59840</v>
       </c>
       <c r="I10" t="n">
-        <v>2237.009345794393</v>
+        <v>2137.009345794393</v>
       </c>
       <c r="J10" t="n">
         <v>57165</v>
@@ -933,7 +933,7 @@
         <v>64906</v>
       </c>
       <c r="I11" t="n">
-        <v>2175.134048257373</v>
+        <v>2075.134048257373</v>
       </c>
       <c r="J11" t="n">
         <v>61922</v>
@@ -979,7 +979,7 @@
         <v>16860</v>
       </c>
       <c r="I12" t="n">
-        <v>663.5182998819363</v>
+        <v>563.5182998819363</v>
       </c>
       <c r="J12" t="n">
         <v>14319</v>
@@ -1025,7 +1025,7 @@
         <v>21988</v>
       </c>
       <c r="I13" t="n">
-        <v>829.4228592983779</v>
+        <v>729.4228592983779</v>
       </c>
       <c r="J13" t="n">
         <v>19337</v>
@@ -1071,7 +1071,7 @@
         <v>19888</v>
       </c>
       <c r="I14" t="n">
-        <v>686.9775474956822</v>
+        <v>586.9775474956822</v>
       </c>
       <c r="J14" t="n">
         <v>16993</v>
@@ -1117,7 +1117,7 @@
         <v>54701</v>
       </c>
       <c r="I15" t="n">
-        <v>1578.216964800923</v>
+        <v>1478.216964800923</v>
       </c>
       <c r="J15" t="n">
         <v>51235</v>
@@ -1163,7 +1163,7 @@
         <v>18471</v>
       </c>
       <c r="I16" t="n">
-        <v>687.6768428890543</v>
+        <v>587.6768428890543</v>
       </c>
       <c r="J16" t="n">
         <v>15785</v>
@@ -1209,7 +1209,7 @@
         <v>16690</v>
       </c>
       <c r="I17" t="n">
-        <v>597.1377459749552</v>
+        <v>497.1377459749552</v>
       </c>
       <c r="J17" t="n">
         <v>13895</v>
@@ -1255,7 +1255,7 @@
         <v>47729</v>
       </c>
       <c r="I18" t="n">
-        <v>1743.843624406284</v>
+        <v>1643.843624406284</v>
       </c>
       <c r="J18" t="n">
         <v>44992</v>
@@ -1301,7 +1301,7 @@
         <v>63027</v>
       </c>
       <c r="I19" t="n">
-        <v>2043.014586709887</v>
+        <v>1943.014586709887</v>
       </c>
       <c r="J19" t="n">
         <v>59942</v>
@@ -1347,7 +1347,7 @@
         <v>43183</v>
       </c>
       <c r="I20" t="n">
-        <v>1492.156185210781</v>
+        <v>1392.156185210781</v>
       </c>
       <c r="J20" t="n">
         <v>40289</v>
@@ -1393,7 +1393,7 @@
         <v>19120</v>
       </c>
       <c r="I21" t="n">
-        <v>691.500904159132</v>
+        <v>591.500904159132</v>
       </c>
       <c r="J21" t="n">
         <v>16355</v>
@@ -1439,7 +1439,7 @@
         <v>38178</v>
       </c>
       <c r="I22" t="n">
-        <v>1514.399047996827</v>
+        <v>1414.399047996827</v>
       </c>
       <c r="J22" t="n">
         <v>35657</v>
@@ -1485,7 +1485,7 @@
         <v>56836</v>
       </c>
       <c r="I23" t="n">
-        <v>1847.123821904452</v>
+        <v>1747.123821904452</v>
       </c>
       <c r="J23" t="n">
         <v>53759</v>
@@ -1531,7 +1531,7 @@
         <v>52114</v>
       </c>
       <c r="I24" t="n">
-        <v>1585.457864313964</v>
+        <v>1485.457864313964</v>
       </c>
       <c r="J24" t="n">
         <v>48827</v>
@@ -1577,7 +1577,7 @@
         <v>20123</v>
       </c>
       <c r="I25" t="n">
-        <v>546.9692851318293</v>
+        <v>446.9692851318293</v>
       </c>
       <c r="J25" t="n">
         <v>16444</v>
@@ -1623,7 +1623,7 @@
         <v>49856</v>
       </c>
       <c r="I26" t="n">
-        <v>1708.567511994517</v>
+        <v>1608.567511994517</v>
       </c>
       <c r="J26" t="n">
         <v>46938</v>
@@ -1669,7 +1669,7 @@
         <v>55790</v>
       </c>
       <c r="I27" t="n">
-        <v>2305.371900826446</v>
+        <v>2205.371900826446</v>
       </c>
       <c r="J27" t="n">
         <v>53370</v>
@@ -1715,7 +1715,7 @@
         <v>45017</v>
       </c>
       <c r="I28" t="n">
-        <v>1760.539694955025</v>
+        <v>1660.539694955025</v>
       </c>
       <c r="J28" t="n">
         <v>42460</v>
@@ -1761,7 +1761,7 @@
         <v>56921</v>
       </c>
       <c r="I29" t="n">
-        <v>1572.403314917127</v>
+        <v>1472.403314917127</v>
       </c>
       <c r="J29" t="n">
         <v>53301</v>
@@ -1807,7 +1807,7 @@
         <v>39744</v>
       </c>
       <c r="I30" t="n">
-        <v>1600.644381796214</v>
+        <v>1500.644381796214</v>
       </c>
       <c r="J30" t="n">
         <v>37261</v>
@@ -1853,7 +1853,7 @@
         <v>22972</v>
       </c>
       <c r="I31" t="n">
-        <v>733.6953050143724</v>
+        <v>633.6953050143724</v>
       </c>
       <c r="J31" t="n">
         <v>19841</v>
@@ -1899,7 +1899,7 @@
         <v>22680</v>
       </c>
       <c r="I32" t="n">
-        <v>735.6470969834577</v>
+        <v>635.6470969834577</v>
       </c>
       <c r="J32" t="n">
         <v>19597</v>
@@ -1945,7 +1945,7 @@
         <v>65475</v>
       </c>
       <c r="I33" t="n">
-        <v>2331.73076923077</v>
+        <v>2231.73076923077</v>
       </c>
       <c r="J33" t="n">
         <v>62667</v>
@@ -1991,7 +1991,7 @@
         <v>21718</v>
       </c>
       <c r="I34" t="n">
-        <v>727.8150134048257</v>
+        <v>627.8150134048257</v>
       </c>
       <c r="J34" t="n">
         <v>18734</v>
@@ -2037,7 +2037,7 @@
         <v>34829</v>
       </c>
       <c r="I35" t="n">
-        <v>1402.133655394525</v>
+        <v>1302.133655394525</v>
       </c>
       <c r="J35" t="n">
         <v>32345</v>
@@ -2083,7 +2083,7 @@
         <v>59283</v>
       </c>
       <c r="I36" t="n">
-        <v>1777.6011994003</v>
+        <v>1677.6011994003</v>
       </c>
       <c r="J36" t="n">
         <v>55948</v>
@@ -2129,7 +2129,7 @@
         <v>20057</v>
       </c>
       <c r="I37" t="n">
-        <v>641.4134953629678</v>
+        <v>541.4134953629678</v>
       </c>
       <c r="J37" t="n">
         <v>16930</v>
@@ -2175,7 +2175,7 @@
         <v>20455</v>
       </c>
       <c r="I38" t="n">
-        <v>704.3732782369145</v>
+        <v>604.3732782369145</v>
       </c>
       <c r="J38" t="n">
         <v>17551</v>
@@ -2221,7 +2221,7 @@
         <v>64302</v>
       </c>
       <c r="I39" t="n">
-        <v>2774.029335634167</v>
+        <v>2674.029335634167</v>
       </c>
       <c r="J39" t="n">
         <v>61984</v>
@@ -2267,7 +2267,7 @@
         <v>49506</v>
       </c>
       <c r="I40" t="n">
-        <v>1419.323394495413</v>
+        <v>1319.323394495413</v>
       </c>
       <c r="J40" t="n">
         <v>46018</v>
@@ -2313,7 +2313,7 @@
         <v>52250</v>
       </c>
       <c r="I41" t="n">
-        <v>1810.464310464311</v>
+        <v>1710.464310464311</v>
       </c>
       <c r="J41" t="n">
         <v>49364</v>
@@ -2359,7 +2359,7 @@
         <v>41313</v>
       </c>
       <c r="I42" t="n">
-        <v>1740.960809102402</v>
+        <v>1640.960809102402</v>
       </c>
       <c r="J42" t="n">
         <v>38940</v>
@@ -2405,7 +2405,7 @@
         <v>57625</v>
       </c>
       <c r="I43" t="n">
-        <v>2089.376359680928</v>
+        <v>1989.376359680928</v>
       </c>
       <c r="J43" t="n">
         <v>54867</v>
@@ -2451,7 +2451,7 @@
         <v>16029</v>
       </c>
       <c r="I44" t="n">
-        <v>614.8446490218643</v>
+        <v>514.8446490218643</v>
       </c>
       <c r="J44" t="n">
         <v>13422</v>
@@ -2497,7 +2497,7 @@
         <v>49191</v>
       </c>
       <c r="I45" t="n">
-        <v>1563.604577240941</v>
+        <v>1463.604577240941</v>
       </c>
       <c r="J45" t="n">
         <v>46045</v>
@@ -2543,7 +2543,7 @@
         <v>59870</v>
       </c>
       <c r="I46" t="n">
-        <v>1761.400411885849</v>
+        <v>1661.400411885849</v>
       </c>
       <c r="J46" t="n">
         <v>56471</v>
@@ -2589,7 +2589,7 @@
         <v>48254</v>
       </c>
       <c r="I47" t="n">
-        <v>1729.534050179212</v>
+        <v>1629.534050179212</v>
       </c>
       <c r="J47" t="n">
         <v>45464</v>
@@ -2635,7 +2635,7 @@
         <v>43397</v>
       </c>
       <c r="I48" t="n">
-        <v>1347.732919254658</v>
+        <v>1247.732919254658</v>
       </c>
       <c r="J48" t="n">
         <v>40177</v>
@@ -2681,7 +2681,7 @@
         <v>16372</v>
       </c>
       <c r="I49" t="n">
-        <v>698.4641638225255</v>
+        <v>598.4641638225255</v>
       </c>
       <c r="J49" t="n">
         <v>14028</v>
@@ -2727,7 +2727,7 @@
         <v>50233</v>
       </c>
       <c r="I50" t="n">
-        <v>1709.186798230691</v>
+        <v>1609.186798230691</v>
       </c>
       <c r="J50" t="n">
         <v>47294</v>
@@ -2773,7 +2773,7 @@
         <v>41460</v>
       </c>
       <c r="I51" t="n">
-        <v>1345.230369889682</v>
+        <v>1245.230369889682</v>
       </c>
       <c r="J51" t="n">
         <v>38378</v>
@@ -2819,7 +2819,7 @@
         <v>50364</v>
       </c>
       <c r="I52" t="n">
-        <v>2154.148845166809</v>
+        <v>2054.148845166809</v>
       </c>
       <c r="J52" t="n">
         <v>48026</v>
@@ -2865,7 +2865,7 @@
         <v>44223</v>
       </c>
       <c r="I53" t="n">
-        <v>1362.384473197782</v>
+        <v>1262.384473197782</v>
       </c>
       <c r="J53" t="n">
         <v>40977</v>
@@ -2911,7 +2911,7 @@
         <v>17006</v>
       </c>
       <c r="I54" t="n">
-        <v>716.3437236731255</v>
+        <v>616.3437236731255</v>
       </c>
       <c r="J54" t="n">
         <v>14632</v>
@@ -2957,7 +2957,7 @@
         <v>15562</v>
       </c>
       <c r="I55" t="n">
-        <v>497.3473953339725</v>
+        <v>397.3473953339725</v>
       </c>
       <c r="J55" t="n">
         <v>12433</v>
@@ -3003,7 +3003,7 @@
         <v>21824</v>
       </c>
       <c r="I56" t="n">
-        <v>742.565498468867</v>
+        <v>642.565498468867</v>
       </c>
       <c r="J56" t="n">
         <v>18885</v>
@@ -3049,7 +3049,7 @@
         <v>46490</v>
       </c>
       <c r="I57" t="n">
-        <v>1759.651778955337</v>
+        <v>1659.651778955337</v>
       </c>
       <c r="J57" t="n">
         <v>43848</v>
@@ -3095,7 +3095,7 @@
         <v>38782</v>
       </c>
       <c r="I58" t="n">
-        <v>1350.818530128875</v>
+        <v>1250.818530128875</v>
       </c>
       <c r="J58" t="n">
         <v>35911</v>
@@ -3141,7 +3141,7 @@
         <v>19350</v>
       </c>
       <c r="I59" t="n">
-        <v>570.4599056603773</v>
+        <v>470.4599056603773</v>
       </c>
       <c r="J59" t="n">
         <v>15958</v>
@@ -3187,7 +3187,7 @@
         <v>16652</v>
       </c>
       <c r="I60" t="n">
-        <v>515.8612143742255</v>
+        <v>415.8612143742255</v>
       </c>
       <c r="J60" t="n">
         <v>13424</v>
@@ -3233,7 +3233,7 @@
         <v>23764</v>
       </c>
       <c r="I61" t="n">
-        <v>748.4724409448819</v>
+        <v>648.4724409448819</v>
       </c>
       <c r="J61" t="n">
         <v>20589</v>
@@ -3279,7 +3279,7 @@
         <v>42803</v>
       </c>
       <c r="I62" t="n">
-        <v>1489.318023660404</v>
+        <v>1389.318023660404</v>
       </c>
       <c r="J62" t="n">
         <v>39929</v>
@@ -3325,7 +3325,7 @@
         <v>41110</v>
       </c>
       <c r="I63" t="n">
-        <v>1472.421203438395</v>
+        <v>1372.421203438395</v>
       </c>
       <c r="J63" t="n">
         <v>38318</v>
@@ -3371,7 +3371,7 @@
         <v>19448</v>
       </c>
       <c r="I64" t="n">
-        <v>495.6167176350663</v>
+        <v>395.6167176350663</v>
       </c>
       <c r="J64" t="n">
         <v>15524</v>
@@ -3417,7 +3417,7 @@
         <v>68828</v>
       </c>
       <c r="I65" t="n">
-        <v>2820.819672131147</v>
+        <v>2720.819672131147</v>
       </c>
       <c r="J65" t="n">
         <v>66388</v>
@@ -3463,7 +3463,7 @@
         <v>19529</v>
       </c>
       <c r="I66" t="n">
-        <v>662</v>
+        <v>562</v>
       </c>
       <c r="J66" t="n">
         <v>16579</v>
@@ -3509,7 +3509,7 @@
         <v>29008</v>
       </c>
       <c r="I67" t="n">
-        <v>1178.229082047116</v>
+        <v>1078.229082047116</v>
       </c>
       <c r="J67" t="n">
         <v>26546</v>
@@ -3555,7 +3555,7 @@
         <v>55684</v>
       </c>
       <c r="I68" t="n">
-        <v>1805.577172503243</v>
+        <v>1705.577172503243</v>
       </c>
       <c r="J68" t="n">
         <v>52600</v>
@@ -3601,7 +3601,7 @@
         <v>45418</v>
       </c>
       <c r="I69" t="n">
-        <v>1429.587661315707</v>
+        <v>1329.587661315707</v>
       </c>
       <c r="J69" t="n">
         <v>42241</v>
@@ -3647,7 +3647,7 @@
         <v>18297</v>
       </c>
       <c r="I70" t="n">
-        <v>609.2907092907093</v>
+        <v>509.2907092907093</v>
       </c>
       <c r="J70" t="n">
         <v>15294</v>
@@ -3693,7 +3693,7 @@
         <v>18966</v>
       </c>
       <c r="I71" t="n">
-        <v>513.0105490938598</v>
+        <v>413.0105490938599</v>
       </c>
       <c r="J71" t="n">
         <v>15269</v>
@@ -3739,7 +3739,7 @@
         <v>18838</v>
       </c>
       <c r="I72" t="n">
-        <v>659.3629681484074</v>
+        <v>559.3629681484074</v>
       </c>
       <c r="J72" t="n">
         <v>15981</v>
@@ -3785,7 +3785,7 @@
         <v>52078</v>
       </c>
       <c r="I73" t="n">
-        <v>1643.876262626263</v>
+        <v>1543.876262626263</v>
       </c>
       <c r="J73" t="n">
         <v>48910</v>
@@ -3831,7 +3831,7 @@
         <v>25321</v>
       </c>
       <c r="I74" t="n">
-        <v>860.3805640502887</v>
+        <v>760.3805640502889</v>
       </c>
       <c r="J74" t="n">
         <v>22378</v>
@@ -3877,7 +3877,7 @@
         <v>40545</v>
       </c>
       <c r="I75" t="n">
-        <v>1460.028808066259</v>
+        <v>1360.028808066259</v>
       </c>
       <c r="J75" t="n">
         <v>37768</v>
@@ -3923,7 +3923,7 @@
         <v>58951</v>
       </c>
       <c r="I76" t="n">
-        <v>1770.832081706218</v>
+        <v>1670.832081706218</v>
       </c>
       <c r="J76" t="n">
         <v>55622</v>
@@ -3969,7 +3969,7 @@
         <v>40921</v>
       </c>
       <c r="I77" t="n">
-        <v>1433.812193412754</v>
+        <v>1333.812193412754</v>
       </c>
       <c r="J77" t="n">
         <v>38067</v>
@@ -4015,7 +4015,7 @@
         <v>49609</v>
       </c>
       <c r="I78" t="n">
-        <v>1941.643835616439</v>
+        <v>1841.643835616439</v>
       </c>
       <c r="J78" t="n">
         <v>47054</v>
@@ -4061,7 +4061,7 @@
         <v>45550</v>
       </c>
       <c r="I79" t="n">
-        <v>1440.543959519292</v>
+        <v>1340.543959519292</v>
       </c>
       <c r="J79" t="n">
         <v>42388</v>
@@ -4107,7 +4107,7 @@
         <v>19563</v>
       </c>
       <c r="I80" t="n">
-        <v>668.1352459016393</v>
+        <v>568.1352459016393</v>
       </c>
       <c r="J80" t="n">
         <v>16635</v>
@@ -4153,7 +4153,7 @@
         <v>41361</v>
       </c>
       <c r="I81" t="n">
-        <v>1818.065934065934</v>
+        <v>1718.065934065934</v>
       </c>
       <c r="J81" t="n">
         <v>39086</v>
@@ -4199,7 +4199,7 @@
         <v>57530</v>
       </c>
       <c r="I82" t="n">
-        <v>1751.293759512938</v>
+        <v>1651.293759512938</v>
       </c>
       <c r="J82" t="n">
         <v>54245</v>
@@ -4245,7 +4245,7 @@
         <v>54768</v>
       </c>
       <c r="I83" t="n">
-        <v>1702.455704072117</v>
+        <v>1602.455704072117</v>
       </c>
       <c r="J83" t="n">
         <v>51551</v>
@@ -4291,7 +4291,7 @@
         <v>18754</v>
       </c>
       <c r="I84" t="n">
-        <v>602.0545746388443</v>
+        <v>502.0545746388443</v>
       </c>
       <c r="J84" t="n">
         <v>15639</v>
@@ -4337,7 +4337,7 @@
         <v>21286</v>
       </c>
       <c r="I85" t="n">
-        <v>765.9589780496582</v>
+        <v>665.9589780496582</v>
       </c>
       <c r="J85" t="n">
         <v>18507</v>
@@ -4383,7 +4383,7 @@
         <v>48796</v>
       </c>
       <c r="I86" t="n">
-        <v>1489.044858101923</v>
+        <v>1389.044858101923</v>
       </c>
       <c r="J86" t="n">
         <v>45519</v>
@@ -4429,7 +4429,7 @@
         <v>19708</v>
       </c>
       <c r="I87" t="n">
-        <v>717.959927140255</v>
+        <v>617.959927140255</v>
       </c>
       <c r="J87" t="n">
         <v>16963</v>
@@ -4475,7 +4475,7 @@
         <v>56089</v>
       </c>
       <c r="I88" t="n">
-        <v>1407.856425702811</v>
+        <v>1307.856425702811</v>
       </c>
       <c r="J88" t="n">
         <v>52105</v>
@@ -4521,7 +4521,7 @@
         <v>19752</v>
       </c>
       <c r="I89" t="n">
-        <v>605.5180870631515</v>
+        <v>505.5180870631514</v>
       </c>
       <c r="J89" t="n">
         <v>16490</v>
@@ -4567,7 +4567,7 @@
         <v>20949</v>
       </c>
       <c r="I90" t="n">
-        <v>770.7505518763796</v>
+        <v>670.7505518763796</v>
       </c>
       <c r="J90" t="n">
         <v>18231</v>
@@ -4613,7 +4613,7 @@
         <v>45666</v>
       </c>
       <c r="I91" t="n">
-        <v>1789.420062695925</v>
+        <v>1689.420062695925</v>
       </c>
       <c r="J91" t="n">
         <v>43114</v>
@@ -4659,7 +4659,7 @@
         <v>40779</v>
       </c>
       <c r="I92" t="n">
-        <v>1327.44140625</v>
+        <v>1227.44140625</v>
       </c>
       <c r="J92" t="n">
         <v>37707</v>
@@ -4705,7 +4705,7 @@
         <v>47482</v>
       </c>
       <c r="I93" t="n">
-        <v>1774.364723467863</v>
+        <v>1674.364723467863</v>
       </c>
       <c r="J93" t="n">
         <v>44806</v>
@@ -4751,7 +4751,7 @@
         <v>18215</v>
       </c>
       <c r="I94" t="n">
-        <v>713.4743439091264</v>
+        <v>613.4743439091264</v>
       </c>
       <c r="J94" t="n">
         <v>15662</v>
@@ -4797,7 +4797,7 @@
         <v>50650</v>
       </c>
       <c r="I95" t="n">
-        <v>1886.405959031658</v>
+        <v>1786.405959031658</v>
       </c>
       <c r="J95" t="n">
         <v>47965</v>
@@ -4843,7 +4843,7 @@
         <v>48933</v>
       </c>
       <c r="I96" t="n">
-        <v>1636.555183946488</v>
+        <v>1536.555183946488</v>
       </c>
       <c r="J96" t="n">
         <v>45943</v>
@@ -4889,7 +4889,7 @@
         <v>42026</v>
       </c>
       <c r="I97" t="n">
-        <v>1498.25311942959</v>
+        <v>1398.25311942959</v>
       </c>
       <c r="J97" t="n">
         <v>39221</v>
@@ -4935,7 +4935,7 @@
         <v>15735</v>
       </c>
       <c r="I98" t="n">
-        <v>552.8812368236121</v>
+        <v>452.8812368236121</v>
       </c>
       <c r="J98" t="n">
         <v>12889</v>
@@ -4981,7 +4981,7 @@
         <v>39856</v>
       </c>
       <c r="I99" t="n">
-        <v>1476.695072248981</v>
+        <v>1376.695072248981</v>
       </c>
       <c r="J99" t="n">
         <v>37157</v>
@@ -5027,7 +5027,7 @@
         <v>20669</v>
       </c>
       <c r="I100" t="n">
-        <v>712.4784557049293</v>
+        <v>612.4784557049293</v>
       </c>
       <c r="J100" t="n">
         <v>17768</v>
@@ -5073,7 +5073,7 @@
         <v>20541</v>
       </c>
       <c r="I101" t="n">
-        <v>681.2935323383084</v>
+        <v>581.2935323383084</v>
       </c>
       <c r="J101" t="n">
         <v>17526</v>
@@ -5119,7 +5119,7 @@
         <v>33647</v>
       </c>
       <c r="I102" t="n">
-        <v>1557.731481481482</v>
+        <v>1457.731481481482</v>
       </c>
       <c r="J102" t="n">
         <v>31487</v>
@@ -5165,7 +5165,7 @@
         <v>41319</v>
       </c>
       <c r="I103" t="n">
-        <v>1341.961675868788</v>
+        <v>1241.961675868788</v>
       </c>
       <c r="J103" t="n">
         <v>38240</v>
@@ -5211,7 +5211,7 @@
         <v>45632</v>
       </c>
       <c r="I104" t="n">
-        <v>2168.821292775665</v>
+        <v>2068.821292775665</v>
       </c>
       <c r="J104" t="n">
         <v>43528</v>
@@ -5257,7 +5257,7 @@
         <v>43773</v>
       </c>
       <c r="I105" t="n">
-        <v>1477.819041188386</v>
+        <v>1377.819041188386</v>
       </c>
       <c r="J105" t="n">
         <v>40811</v>
@@ -5303,7 +5303,7 @@
         <v>36821</v>
       </c>
       <c r="I106" t="n">
-        <v>1301.095406360424</v>
+        <v>1201.095406360424</v>
       </c>
       <c r="J106" t="n">
         <v>33991</v>
@@ -5349,7 +5349,7 @@
         <v>22824</v>
       </c>
       <c r="I107" t="n">
-        <v>707.0631970260223</v>
+        <v>607.0631970260223</v>
       </c>
       <c r="J107" t="n">
         <v>19596</v>
@@ -5395,7 +5395,7 @@
         <v>21953</v>
       </c>
       <c r="I108" t="n">
-        <v>730.549084858569</v>
+        <v>630.549084858569</v>
       </c>
       <c r="J108" t="n">
         <v>18948</v>
@@ -5441,7 +5441,7 @@
         <v>51229</v>
       </c>
       <c r="I109" t="n">
-        <v>1696.324503311258</v>
+        <v>1596.324503311258</v>
       </c>
       <c r="J109" t="n">
         <v>48209</v>
@@ -5487,7 +5487,7 @@
         <v>50583</v>
       </c>
       <c r="I110" t="n">
-        <v>1716.423481506617</v>
+        <v>1616.423481506617</v>
       </c>
       <c r="J110" t="n">
         <v>47636</v>
@@ -5533,7 +5533,7 @@
         <v>50895</v>
       </c>
       <c r="I111" t="n">
-        <v>1625.519003513255</v>
+        <v>1525.519003513255</v>
       </c>
       <c r="J111" t="n">
         <v>47764</v>
@@ -5579,7 +5579,7 @@
         <v>46503</v>
       </c>
       <c r="I112" t="n">
-        <v>1602.998965873837</v>
+        <v>1502.998965873837</v>
       </c>
       <c r="J112" t="n">
         <v>43602</v>
@@ -5625,7 +5625,7 @@
         <v>18089</v>
       </c>
       <c r="I113" t="n">
-        <v>618.2159945317841</v>
+        <v>518.2159945317841</v>
       </c>
       <c r="J113" t="n">
         <v>15163</v>
@@ -5671,7 +5671,7 @@
         <v>56504</v>
       </c>
       <c r="I114" t="n">
-        <v>1830.97861309138</v>
+        <v>1730.97861309138</v>
       </c>
       <c r="J114" t="n">
         <v>53418</v>
@@ -5717,7 +5717,7 @@
         <v>44635</v>
       </c>
       <c r="I115" t="n">
-        <v>1620.733478576616</v>
+        <v>1520.733478576616</v>
       </c>
       <c r="J115" t="n">
         <v>41881</v>
@@ -5763,7 +5763,7 @@
         <v>43924</v>
       </c>
       <c r="I116" t="n">
-        <v>1924.802804557406</v>
+        <v>1824.802804557406</v>
       </c>
       <c r="J116" t="n">
         <v>41642</v>
@@ -5809,7 +5809,7 @@
         <v>19811</v>
       </c>
       <c r="I117" t="n">
-        <v>596.8966556191624</v>
+        <v>496.8966556191624</v>
       </c>
       <c r="J117" t="n">
         <v>16492</v>
@@ -5855,7 +5855,7 @@
         <v>56140</v>
       </c>
       <c r="I118" t="n">
-        <v>1822.135670236936</v>
+        <v>1722.135670236936</v>
       </c>
       <c r="J118" t="n">
         <v>53059</v>
@@ -5901,7 +5901,7 @@
         <v>40462</v>
       </c>
       <c r="I119" t="n">
-        <v>1591.738788355626</v>
+        <v>1491.738788355626</v>
       </c>
       <c r="J119" t="n">
         <v>37920</v>
@@ -5947,7 +5947,7 @@
         <v>54145</v>
       </c>
       <c r="I120" t="n">
-        <v>2142.659279778393</v>
+        <v>2042.659279778393</v>
       </c>
       <c r="J120" t="n">
         <v>51618</v>
@@ -5993,7 +5993,7 @@
         <v>51882</v>
       </c>
       <c r="I121" t="n">
-        <v>1748.634984833165</v>
+        <v>1648.634984833165</v>
       </c>
       <c r="J121" t="n">
         <v>48915</v>
@@ -6039,7 +6039,7 @@
         <v>35022</v>
       </c>
       <c r="I122" t="n">
-        <v>1485.871871022486</v>
+        <v>1385.871871022486</v>
       </c>
       <c r="J122" t="n">
         <v>32665</v>
@@ -6085,7 +6085,7 @@
         <v>49290</v>
       </c>
       <c r="I123" t="n">
-        <v>1736.786469344609</v>
+        <v>1636.786469344609</v>
       </c>
       <c r="J123" t="n">
         <v>46452</v>
@@ -6131,7 +6131,7 @@
         <v>47108</v>
       </c>
       <c r="I124" t="n">
-        <v>1616.609471516815</v>
+        <v>1516.609471516815</v>
       </c>
       <c r="J124" t="n">
         <v>44194</v>
@@ -6177,7 +6177,7 @@
         <v>20703</v>
       </c>
       <c r="I125" t="n">
-        <v>778.8939051918736</v>
+        <v>678.8939051918736</v>
       </c>
       <c r="J125" t="n">
         <v>18045</v>
@@ -6223,7 +6223,7 @@
         <v>18099</v>
       </c>
       <c r="I126" t="n">
-        <v>634.1625788367204</v>
+        <v>534.1625788367204</v>
       </c>
       <c r="J126" t="n">
         <v>15245</v>
@@ -6269,7 +6269,7 @@
         <v>18942</v>
       </c>
       <c r="I127" t="n">
-        <v>686.5530989488946</v>
+        <v>586.5530989488946</v>
       </c>
       <c r="J127" t="n">
         <v>16183</v>
@@ -6315,7 +6315,7 @@
         <v>52072</v>
       </c>
       <c r="I128" t="n">
-        <v>2039.63963963964</v>
+        <v>1939.63963963964</v>
       </c>
       <c r="J128" t="n">
         <v>49519</v>
@@ -6361,7 +6361,7 @@
         <v>55203</v>
       </c>
       <c r="I129" t="n">
-        <v>1918.769551616267</v>
+        <v>1818.769551616267</v>
       </c>
       <c r="J129" t="n">
         <v>52326</v>
@@ -6407,7 +6407,7 @@
         <v>59254</v>
       </c>
       <c r="I130" t="n">
-        <v>1689.592244083262</v>
+        <v>1589.592244083262</v>
       </c>
       <c r="J130" t="n">
         <v>55747</v>
@@ -6453,7 +6453,7 @@
         <v>21603</v>
       </c>
       <c r="I131" t="n">
-        <v>828.3358895705522</v>
+        <v>728.3358895705521</v>
       </c>
       <c r="J131" t="n">
         <v>18995</v>
@@ -6499,7 +6499,7 @@
         <v>36029</v>
       </c>
       <c r="I132" t="n">
-        <v>1776.577909270217</v>
+        <v>1676.577909270217</v>
       </c>
       <c r="J132" t="n">
         <v>34001</v>
@@ -6545,7 +6545,7 @@
         <v>21056</v>
       </c>
       <c r="I133" t="n">
-        <v>759.3220338983051</v>
+        <v>659.3220338983051</v>
       </c>
       <c r="J133" t="n">
         <v>18283</v>
@@ -6591,7 +6591,7 @@
         <v>57432</v>
       </c>
       <c r="I134" t="n">
-        <v>1917.595993322204</v>
+        <v>1817.595993322204</v>
       </c>
       <c r="J134" t="n">
         <v>54437</v>
@@ -6637,7 +6637,7 @@
         <v>18454</v>
       </c>
       <c r="I135" t="n">
-        <v>514.6123814835471</v>
+        <v>414.6123814835472</v>
       </c>
       <c r="J135" t="n">
         <v>14868</v>
@@ -6683,7 +6683,7 @@
         <v>59060</v>
       </c>
       <c r="I136" t="n">
-        <v>1925.660254320183</v>
+        <v>1825.660254320183</v>
       </c>
       <c r="J136" t="n">
         <v>55993</v>
@@ -6729,7 +6729,7 @@
         <v>19426</v>
       </c>
       <c r="I137" t="n">
-        <v>1072.66703478741</v>
+        <v>972.6670347874103</v>
       </c>
       <c r="J137" t="n">
         <v>17615</v>
@@ -6775,7 +6775,7 @@
         <v>47262</v>
       </c>
       <c r="I138" t="n">
-        <v>1727.412280701755</v>
+        <v>1627.412280701755</v>
       </c>
       <c r="J138" t="n">
         <v>44526</v>
@@ -6821,7 +6821,7 @@
         <v>19703</v>
       </c>
       <c r="I139" t="n">
-        <v>633.1298200514138</v>
+        <v>533.1298200514138</v>
       </c>
       <c r="J139" t="n">
         <v>16591</v>
@@ -6867,7 +6867,7 @@
         <v>40255</v>
       </c>
       <c r="I140" t="n">
-        <v>1546.48482520169</v>
+        <v>1446.48482520169</v>
       </c>
       <c r="J140" t="n">
         <v>37652</v>
@@ -6913,7 +6913,7 @@
         <v>62337</v>
       </c>
       <c r="I141" t="n">
-        <v>1953.52554058289</v>
+        <v>1853.52554058289</v>
       </c>
       <c r="J141" t="n">
         <v>59146</v>
@@ -6959,7 +6959,7 @@
         <v>55357</v>
       </c>
       <c r="I142" t="n">
-        <v>1543.267354335099</v>
+        <v>1443.267354335099</v>
       </c>
       <c r="J142" t="n">
         <v>51770</v>
@@ -7005,7 +7005,7 @@
         <v>48954</v>
       </c>
       <c r="I143" t="n">
-        <v>1681.69014084507</v>
+        <v>1581.69014084507</v>
       </c>
       <c r="J143" t="n">
         <v>46043</v>
@@ -7051,7 +7051,7 @@
         <v>48315</v>
       </c>
       <c r="I144" t="n">
-        <v>1473.467520585544</v>
+        <v>1373.467520585544</v>
       </c>
       <c r="J144" t="n">
         <v>45036</v>
@@ -7097,7 +7097,7 @@
         <v>52366</v>
       </c>
       <c r="I145" t="n">
-        <v>1778.132427843803</v>
+        <v>1678.132427843803</v>
       </c>
       <c r="J145" t="n">
         <v>49421</v>
@@ -7143,7 +7143,7 @@
         <v>49376</v>
       </c>
       <c r="I146" t="n">
-        <v>2089.547185780787</v>
+        <v>1989.547185780787</v>
       </c>
       <c r="J146" t="n">
         <v>47013</v>
@@ -7189,7 +7189,7 @@
         <v>34603</v>
       </c>
       <c r="I147" t="n">
-        <v>1537.227898711684</v>
+        <v>1437.227898711684</v>
       </c>
       <c r="J147" t="n">
         <v>32352</v>
@@ -7235,7 +7235,7 @@
         <v>63148</v>
       </c>
       <c r="I148" t="n">
-        <v>1718.312925170068</v>
+        <v>1618.312925170068</v>
       </c>
       <c r="J148" t="n">
         <v>59473</v>
@@ -7281,7 +7281,7 @@
         <v>43377</v>
       </c>
       <c r="I149" t="n">
-        <v>1638.104229607251</v>
+        <v>1538.104229607251</v>
       </c>
       <c r="J149" t="n">
         <v>40729</v>
@@ -7327,7 +7327,7 @@
         <v>22457</v>
       </c>
       <c r="I150" t="n">
-        <v>750.0668002672011</v>
+        <v>650.0668002672011</v>
       </c>
       <c r="J150" t="n">
         <v>19463</v>
@@ -7373,7 +7373,7 @@
         <v>40141</v>
       </c>
       <c r="I151" t="n">
-        <v>1651.213492389963</v>
+        <v>1551.213492389963</v>
       </c>
       <c r="J151" t="n">
         <v>37710</v>
